--- a/data/trans_orig/TAM_HOG-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/TAM_HOG-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de personas que viven habitualmente en el hogar</t>
+          <t>Número medio de personas que viven habitualmente en el hogar (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,42 +716,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 3,02</t>
+          <t>2,85; 3,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 2,95</t>
+          <t>2,78; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 2,78</t>
+          <t>2,56; 2,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 2,39</t>
+          <t>2,2; 2,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 2,98</t>
+          <t>2,82; 2,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 2,85</t>
+          <t>2,71; 2,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 2,67</t>
+          <t>2,5; 2,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,17</t>
+          <t>2,04; 2,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 2,88</t>
+          <t>2,76; 2,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 2,7</t>
+          <t>2,56; 2,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,23</t>
+          <t>2,13; 2,23</t>
         </is>
       </c>
     </row>
@@ -856,22 +856,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 3,38</t>
+          <t>3,27; 3,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 3,42</t>
+          <t>3,3; 3,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,14</t>
+          <t>3,03; 3,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 3,25</t>
+          <t>2,79; 3,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,15</t>
+          <t>3,04; 3,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,06</t>
+          <t>2,89; 3,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 3,44</t>
+          <t>3,37; 3,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,12</t>
+          <t>3,05; 3,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,14</t>
+          <t>2,88; 3,18</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 2,87</t>
+          <t>2,66; 2,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,22</t>
+          <t>3,0; 3,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,21</t>
+          <t>2,99; 3,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 2,93</t>
+          <t>2,77; 2,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,19</t>
+          <t>3,04; 3,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,15</t>
+          <t>2,98; 3,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 3,21</t>
+          <t>3,12; 3,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,27 +1146,27 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 2,98</t>
+          <t>2,89; 2,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 3,07</t>
+          <t>2,7; 3,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 3,27</t>
+          <t>3,17; 3,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 3,19</t>
+          <t>3,11; 3,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 2,96</t>
+          <t>2,88; 2,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 3,19</t>
+          <t>3,13; 3,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 2,93</t>
+          <t>2,74; 2,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/TAM_HOG-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/TAM_HOG-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,21</t>
         </is>
       </c>
     </row>
@@ -716,22 +716,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,02</t>
+          <t>2,86; 3,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 2,94</t>
+          <t>2,78; 2,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 2,77</t>
+          <t>2,56; 2,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 2,39</t>
+          <t>2,23; 2,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 2,86</t>
+          <t>2,7; 2,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 2,68</t>
+          <t>2,51; 2,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,18</t>
+          <t>2,06; 2,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 2,97</t>
+          <t>2,86; 2,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,23</t>
+          <t>2,15; 2,28</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>3,03</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>2,92</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 3,37</t>
+          <t>3,26; 3,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 3,41</t>
+          <t>3,3; 3,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 3,27</t>
+          <t>2,74; 2,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 3,59</t>
+          <t>3,45; 3,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 3,14</t>
+          <t>3,03; 3,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 3,06</t>
+          <t>2,98; 3,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 3,45</t>
+          <t>3,37; 3,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,18</t>
+          <t>2,87; 2,96</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>2,83</t>
         </is>
       </c>
     </row>
@@ -1006,27 +1006,27 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 2,9</t>
+          <t>2,66; 2,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 2,89</t>
+          <t>2,7; 2,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,23</t>
+          <t>3,01; 3,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,22</t>
+          <t>2,99; 3,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 3,01</t>
+          <t>2,8; 3,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 3,19</t>
+          <t>3,04; 3,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,14</t>
+          <t>2,98; 3,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 2,92</t>
+          <t>2,76; 2,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,76</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 3,2</t>
+          <t>3,12; 3,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 3,09</t>
+          <t>2,68; 2,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1171,17 +1171,17 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 2,84</t>
+          <t>2,76; 2,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,22</t>
+          <t>3,16; 3,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 3,2</t>
+          <t>3,13; 3,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 2,94</t>
+          <t>2,74; 2,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/TAM_HOG-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/TAM_HOG-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de personas que viven habitualmente en el hogar (tasa de respuesta: 100,0%)</t>
+          <t>Número medio de personas que conviven habitualmente en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
